--- a/stories/arbres/ATOM-LAN.NOM.001-09.xlsx
+++ b/stories/arbres/ATOM-LAN.NOM.001-09.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Hadrien et papa sont au bord de l'eau. Il y a un seau. Dedans, des galets. Papa dit : on va compter des objets. Hadrien touche un galet. Une. Il en touche un autre. Deux. Encore un. Trois. Encore un. Quatre. Encore un. Cinq. Hadrien dit : cinq galets. Papa sourit. Il dit le nombre. Cinq. Hadrien pose les galets. Une. Deux. Trois. Quatre. Cinq. Les objets sont là. Hadrien les compte. L'eau clapote. Parce qu'il a compté des objets, Hadrien peut dire le nombre. Papa range le seau. Hadrien garde un galet lisse.</t>
+          <t>Hadrien et papa sont au bord de l'eau. Il y a un seau. Dedans, des galets. On va compter des objets. Hadrien touche un galet. Une. Il en touche un autre. Deux. Encore un. Trois. Encore un. Quatre. Encore un. Cinq. Cinq galets. Papa sourit. Il dit le nombre. Cinq. Hadrien pose les galets. Une. Deux. Trois. Quatre. Cinq. Les objets sont là. Hadrien les compte. L'eau clapote. Parce qu'il a compté des objets, Hadrien peut dire le nombre. Papa range le seau. Hadrien garde un galet lisse.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,15 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Hadrien et papa sont au bord de l'eau. Il y a un seau. Dedans, des galets.
+papa|On va compter des objets.
+narrateur|Hadrien touche un galet. Une. Il en touche un autre. Deux. Encore un. Trois. Encore un. Quatre. Encore un. Cinq.
+enfant-m|Cinq galets. Papa sourit. Il dit le nombre. Cinq.
+narrateur|Hadrien pose les galets. Une. Deux. Trois. Quatre. Cinq. Les objets sont là. Hadrien les compte. L'eau clapote. Parce qu'il a compté des objets, Hadrien peut dire le nombre. Papa range le seau. Hadrien garde un galet lisse.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1490,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Hadrien compte les galets. Combien y en a-t-il ?</t>
         </is>
       </c>
     </row>
@@ -1629,6 +1659,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Hadrien a compté des objets. Cinq galets. Il a dit le nombre.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1787,6 +1822,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Papa range le seau. Hadrien garde un galet. Il le touche.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1949,6 +1989,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1967,7 +2012,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1984,6 +2029,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-LAN.NOM.001-09.xlsx
+++ b/stories/arbres/ATOM-LAN.NOM.001-09.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1314,6 +1319,11 @@
 narrateur|Hadrien pose les galets. Une. Deux. Trois. Quatre. Cinq. Les objets sont là. Hadrien les compte. L'eau clapote. Parce qu'il a compté des objets, Hadrien peut dire le nombre. Papa range le seau. Hadrien garde un galet lisse.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1497,6 +1507,7 @@
           <t>narrateur|Hadrien compte les galets. Combien y en a-t-il ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1664,6 +1675,7 @@
           <t>narrateur|Hadrien a compté des objets. Cinq galets. Il a dit le nombre.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1827,6 +1839,7 @@
           <t>narrateur|Papa range le seau. Hadrien garde un galet. Il le touche.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1994,6 +2007,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2012,7 +2026,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2036,6 +2050,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2050,7 +2078,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2237,6 +2265,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-LAN.NOM.001-09.xlsx
+++ b/stories/arbres/ATOM-LAN.NOM.001-09.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Hadrien compte les galets</t>
+          <t>Le seau bleu de Raphaël</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>L'eau tape les galets. Raphaël remplit le seau bleu, touche chaque pierre, dit le nombre. Il en garde une, toute lisse.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Hadrien et papa sont au bord de l'eau. Il y a un seau. Dedans, des galets. On va compter des objets. Hadrien touche un galet. Une. Il en touche un autre. Deux. Encore un. Trois. Encore un. Quatre. Encore un. Cinq. Cinq galets. Papa sourit. Il dit le nombre. Cinq. Hadrien pose les galets. Une. Deux. Trois. Quatre. Cinq. Les objets sont là. Hadrien les compte. L'eau clapote. Parce qu'il a compté des objets, Hadrien peut dire le nombre. Papa range le seau. Hadrien garde un galet lisse.</t>
+          <t>L'eau de la rivière tape les galets. Ça fait un petit choc, tout rond. Un seau bleu attend dans l'herbe. Le vent est frais sur les joues. Une libellule passe, puis plus. Maman plie un coin de la couverture. La couverture sent le soleil un peu. Un oiseau crie, très loin. L'eau est claire, aujourd'hui, Raphaël. Tu entends les galets ? Oui, papa. Ça cloche. Je vous vois d'ici. Le seau est près de toi. En ce moment, Raphaël prend le seau. Le plastique est un peu froid. Dedans, déjà, des galets. On va compter des objets, Raphaël. Tu touches, et tu dis le nombre. Raphaël touche un galet. Un. Il est lisse, un peu gris. Encore un. Deux. Encore un. Trois. Encore un. Quatre. Encore un. Cinq. Cinq galets. Bravo. Tu as dit le nombre. Raphaël pose les galets sur l'herbe. Un. Deux. Trois. Quatre. Cinq. Tu as compté des objets. Cinq galets. C'est du bon travail, Raphaël. Les lisses ensemble ? Oui, maman. Les rudes ensemble. Raphaël range les lisses d'un côté. L'eau clapote encore. C'est un son. Quel nom ? L'eau. Oui. Le nom du son, c'est l'eau. Tu as fini de compter ? Oui, papa. Bravo, Raphaël.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,18 +1324,64 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Hadrien et papa sont au bord de l'eau. Il y a un seau. Dedans, des galets.
-papa|On va compter des objets.
-narrateur|Hadrien touche un galet. Une. Il en touche un autre. Deux. Encore un. Trois. Encore un. Quatre. Encore un. Cinq.
-enfant-m|Cinq galets. Papa sourit. Il dit le nombre. Cinq.
-narrateur|Hadrien pose les galets. Une. Deux. Trois. Quatre. Cinq. Les objets sont là. Hadrien les compte. L'eau clapote. Parce qu'il a compté des objets, Hadrien peut dire le nombre. Papa range le seau. Hadrien garde un galet lisse.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>enfants_parc</t>
-        </is>
-      </c>
+          <t>narrateur|L'eau de la rivière tape les galets.
+narrateur|Ça fait un petit choc, tout rond.
+narrateur|Un seau bleu attend dans l'herbe.
+narrateur|Le vent est frais sur les joues.
+narrateur|Une libellule passe, puis plus.
+narrateur|Maman plie un coin de la couverture.
+narrateur|La couverture sent le soleil un peu.
+narrateur|Un oiseau crie, très loin.
+papa|L'eau est claire, aujourd'hui, Raphaël.
+papa|Tu entends les galets ?
+enfant-m|Oui, papa.
+enfant-m|Ça cloche.
+maman|Je vous vois d'ici.
+maman|Le seau est près de toi.
+narrateur|En ce moment, Raphaël prend le seau.
+narrateur|Le plastique est un peu froid.
+narrateur|Dedans, déjà, des galets.
+papa|On va compter des objets, Raphaël.
+papa|Tu touches, et tu dis le nombre.
+narrateur|Raphaël touche un galet.
+enfant-m|Un.
+narrateur|Il est lisse, un peu gris.
+narrateur|Encore un.
+enfant-m|Deux.
+narrateur|Encore un.
+enfant-m|Trois.
+narrateur|Encore un.
+enfant-m|Quatre.
+narrateur|Encore un.
+enfant-m|Cinq.
+enfant-m|Cinq galets.
+papa|Bravo.
+papa|Tu as dit le nombre.
+narrateur|Raphaël pose les galets sur l'herbe.
+enfant-m|Un.
+enfant-m|Deux.
+enfant-m|Trois.
+enfant-m|Quatre.
+enfant-m|Cinq.
+papa|Tu as compté des objets.
+papa|Cinq galets.
+papa|C'est du bon travail, Raphaël.
+maman|Les lisses ensemble ?
+enfant-m|Oui, maman.
+enfant-m|Les rudes ensemble.
+narrateur|Raphaël range les lisses d'un côté.
+narrateur|L'eau clapote encore.
+papa|C'est un son.
+papa|Quel nom ?
+enfant-m|L'eau.
+papa|Oui.
+papa|Le nom du son, c'est l'eau.
+papa|Tu as fini de compter ?
+enfant-m|Oui, papa.
+maman|Bravo, Raphaël.</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1348,7 +1406,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Hadrien compte les galets. Combien y en a-t-il ?</t>
+          <t>Raphaël compte les galets. Combien y en a-t-il ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1504,7 +1562,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Hadrien compte les galets. Combien y en a-t-il ?</t>
+          <t>narrateur|Raphaël compte les galets.
+narrateur|Combien y en a-t-il ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1532,7 +1591,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Hadrien a compté des objets. Cinq galets. Il a dit le nombre.</t>
+          <t>Raphaël a compté des objets. Cinq galets. Il a dit le nombre. Cinq. Bravo. C'est du bon travail, Raphaël. Tu gardes un galet ? Oui. Le plus lisse. Le galet est tiède dans sa main.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1672,7 +1731,16 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Hadrien a compté des objets. Cinq galets. Il a dit le nombre.</t>
+          <t>narrateur|Raphaël a compté des objets.
+narrateur|Cinq galets.
+narrateur|Il a dit le nombre.
+papa|Cinq.
+papa|Bravo.
+maman|C'est du bon travail, Raphaël.
+maman|Tu gardes un galet ?
+enfant-m|Oui.
+enfant-m|Le plus lisse.
+narrateur|Le galet est tiède dans sa main.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1700,7 +1768,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Papa range le seau. Hadrien garde un galet. Il le touche.</t>
+          <t>Papa range le seau. L'eau continue de taper les pierres. On rejoint maman ? Oui, papa. Raphaël garde un galet lisse. Il le touche encore. Il est doux, celui-là. J'ai compté des objets. Oui. Tu as dit le nombre. Viens sur la couverture.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1836,7 +1904,17 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Papa range le seau. Hadrien garde un galet. Il le touche.</t>
+          <t>narrateur|Papa range le seau.
+narrateur|L'eau continue de taper les pierres.
+papa|On rejoint maman ?
+enfant-m|Oui, papa.
+narrateur|Raphaël garde un galet lisse.
+narrateur|Il le touche encore.
+maman|Il est doux, celui-là.
+enfant-m|J'ai compté des objets.
+papa|Oui.
+papa|Tu as dit le nombre.
+maman|Viens sur la couverture.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1864,7 +1942,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Cinq galets. J'ai dit le nombre. Bravo, Raphaël. Tu as fait du bon travail. Le seau bleu repose dans l'herbe. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2004,7 +2082,12 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|Cinq galets.
+enfant-m|J'ai dit le nombre.
+papa|Bravo, Raphaël.
+maman|Tu as fait du bon travail.
+narrateur|Le seau bleu repose dans l'herbe.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2026,7 +2109,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2064,6 +2147,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-LAN.NOM.001-09.xlsx
+++ b/stories/arbres/ATOM-LAN.NOM.001-09.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>L'eau de la rivière tape les galets. Ça fait un petit choc, tout rond. Un seau bleu attend dans l'herbe. Le vent est frais sur les joues. Une libellule passe, puis plus. Maman plie un coin de la couverture. La couverture sent le soleil un peu. Un oiseau crie, très loin. L'eau est claire, aujourd'hui, Raphaël. Tu entends les galets ? Oui, papa. Ça cloche. Je vous vois d'ici. Le seau est près de toi. En ce moment, Raphaël prend le seau. Le plastique est un peu froid. Dedans, déjà, des galets. On va compter des objets, Raphaël. Tu touches, et tu dis le nombre. Raphaël touche un galet. Un. Il est lisse, un peu gris. Encore un. Deux. Encore un. Trois. Encore un. Quatre. Encore un. Cinq. Cinq galets. Bravo. Tu as dit le nombre. Raphaël pose les galets sur l'herbe. Un. Deux. Trois. Quatre. Cinq. Tu as compté des objets. Cinq galets. C'est du bon travail, Raphaël. Les lisses ensemble ? Oui, maman. Les rudes ensemble. Raphaël range les lisses d'un côté. L'eau clapote encore. C'est un son. Quel nom ? L'eau. Oui. Le nom du son, c'est l'eau. Tu as fini de compter ? Oui, papa. Bravo, Raphaël.</t>
+          <t>L'eau de la rivière tape les galets. Ça fait un petit choc, tout rond. Un seau bleu attend dans l'herbe. Le vent est frais sur les joues. Une libellule passe, puis plus. Maman plie un coin de la couverture. La couverture sent le soleil un peu. Un oiseau crie, très loin. L'eau est claire, aujourd'hui, Raphaël. Tu entends les galets ? Oui, papa. Ça cloche. Je vous vois d'ici. Le seau est près de toi. En ce moment, Raphaël prend le seau. Le plastique est un peu froid. Dedans, déjà, des galets. On va compter des objets, Raphaël. Tu touches, et tu dis le nombre. Raphaël touche un galet. Un. Il est lisse, un peu gris. Encore un. Deux. Encore un. Trois. Encore un. Quatre. Encore un. Cinq. Cinq galets. Bravo. Tu as dit le nombre. Raphaël pose les galets sur l'herbe. Un. Deux. Trois. Quatre. Cinq. Tu as compté des objets. Cinq galets. Les lisses ensemble ? Oui, maman. Les rudes ensemble. Raphaël range les lisses d'un côté. L'eau clapote encore. C'est un son. Quel nom ? L'eau. Oui. Le nom du son, c'est l'eau. Tu as fini de compter ? Oui, papa. Bravo, Raphaël.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Hadrien et papa sont au bord de l'eau. Il y a un seau. Dedans, des galets. Papa dit : on va &lt;emphasis level="moderate"&gt;compter&lt;/emphasis&gt; des objets. Hadrien touche un galet. Une. Il en touche un autre. Deux. Encore un. Trois. Encore un. Quatre. Encore un. Cinq. Hadrien dit : cinq galets. Papa sourit. Il dit le nombre. Cinq. Hadrien pose les galets. Une. Deux. Trois. Quatre. Cinq. Les objets sont là. Hadrien les compte. L'eau clapote. Parce qu'il a compté des objets, Hadrien peut dire le nombre. Papa range le seau. Hadrien garde un galet lisse.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>L'eau de la rivière tape les galets. Ça fait un petit choc, tout rond. Un seau bleu attend dans l'herbe. Le vent est frais sur les joues. Une libellule passe, puis plus. Maman plie un coin de la couverture. La couverture sent le soleil un peu. Un oiseau crie, très loin. L'eau est claire, aujourd'hui, Raphaël. Tu entends les galets ? Oui, papa. Ça cloche. Je vous vois d'ici. Le seau est près de toi. En ce moment, Raphaël prend le seau. Le plastique est un peu froid. Dedans, déjà, des galets. On va compter des objets, Raphaël. Tu touches, et tu dis le nombre. Raphaël touche un galet. Un. Il est lisse, un peu gris. Encore un. Deux. Encore un. Trois. Encore un. Quatre. Encore un. Cinq. Cinq galets. Bravo. Tu as dit le nombre. Raphaël pose les galets sur l'herbe. Un. Deux. Trois. Quatre. Cinq. Tu as compté des objets. Cinq galets. Les lisses ensemble ? Oui, maman. Les rudes ensemble. Raphaël range les lisses d'un côté. L'eau clapote encore. C'est un son. Quel nom ? L'eau. Oui. Le nom du son, c'est l'eau. Tu as fini de compter ? Oui, papa. Bravo, Raphaël.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1365,7 +1365,6 @@
 enfant-m|Cinq.
 papa|Tu as compté des objets.
 papa|Cinq galets.
-papa|C'est du bon travail, Raphaël.
 maman|Les lisses ensemble ?
 enfant-m|Oui, maman.
 enfant-m|Les rudes ensemble.
@@ -1381,7 +1380,6 @@
 maman|Bravo, Raphaël.</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1411,7 +1409,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Hadrien compte les galets. Combien y en a-t-il ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Raphaël compte les galets. Combien y en a-t-il ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1566,7 +1564,6 @@
 narrateur|Combien y en a-t-il ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1591,12 +1588,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Raphaël a compté des objets. Cinq galets. Il a dit le nombre. Cinq. Bravo. C'est du bon travail, Raphaël. Tu gardes un galet ? Oui. Le plus lisse. Le galet est tiède dans sa main.</t>
+          <t>Raphaël a compté des objets. Cinq galets. Il a dit le nombre. Cinq. Bravo. Tu gardes un galet ? Oui. Le plus lisse. Le galet est tiède dans sa main.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Hadrien a compté des objets. Cinq galets. Il a dit le nombre.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Raphaël a compté des objets. Cinq galets. Il a dit le nombre. Cinq. Bravo. Tu gardes un galet ? Oui. Le plus lisse. Le galet est tiède dans sa main.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1736,14 +1733,12 @@
 narrateur|Il a dit le nombre.
 papa|Cinq.
 papa|Bravo.
-maman|C'est du bon travail, Raphaël.
 maman|Tu gardes un galet ?
 enfant-m|Oui.
 enfant-m|Le plus lisse.
 narrateur|Le galet est tiède dans sa main.</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1773,7 +1768,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Papa range le seau. Hadrien garde un galet. Il le touche.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Papa range le seau. L'eau continue de taper les pierres. On rejoint maman ? Oui, papa. Raphaël garde un galet lisse. Il le touche encore. Il est doux, celui-là. J'ai compté des objets. Oui. Tu as dit le nombre. Viens sur la couverture.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1917,7 +1912,6 @@
 maman|Viens sur la couverture.</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1942,12 +1936,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Cinq galets. J'ai dit le nombre. Bravo, Raphaël. Tu as fait du bon travail. Le seau bleu repose dans l'herbe. L'histoire est finie.</t>
+          <t>Cinq galets. J'ai dit le nombre. Bravo, Raphaël. Le seau bleu repose dans l'herbe.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Cinq galets. J'ai dit le nombre. Bravo, Raphaël. Le seau bleu repose dans l'herbe.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2085,12 +2079,9 @@
           <t>enfant-m|Cinq galets.
 enfant-m|J'ai dit le nombre.
 papa|Bravo, Raphaël.
-maman|Tu as fait du bon travail.
-narrateur|Le seau bleu repose dans l'herbe.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+narrateur|Le seau bleu repose dans l'herbe.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2109,7 +2100,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2154,6 +2145,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-LAN.NOM.001-09.xlsx
+++ b/stories/arbres/ATOM-LAN.NOM.001-09.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Hadrien, papa</t>
+          <t>Raphaël, papa, maman</t>
         </is>
       </c>
     </row>
